--- a/excel_reports/backtest_compare/s4/compare_s4_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s4/compare_s4_M15_20260528_0800_20260608_1000.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Gap Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mismatches'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 20:51:20</t>
+          <t>2026-06-16 10:38:08</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK9"/>
+  <dimension ref="A1:BK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -812,7 +812,7 @@
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
     <col width="15" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="15" customWidth="1" min="43" max="43"/>
@@ -1194,24 +1194,24 @@
       <c r="AB2" s="8" t="inlineStr"/>
       <c r="AC2" s="8" t="inlineStr"/>
       <c r="AD2" s="9" t="n">
-        <v>46171.625</v>
+        <v>46170.875</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>46171.875</v>
+        <v>46170.90625</v>
       </c>
       <c r="AF2" s="8" t="n">
-        <v>4544.3</v>
+        <v>4477.22</v>
       </c>
       <c r="AG2" s="8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH2" s="8" t="n">
-        <v>4520.79</v>
+        <v>4448.91</v>
       </c>
       <c r="AI2" s="8" t="n">
-        <v>23.51</v>
+        <v>-28.31</v>
       </c>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
       <c r="AM2" s="8" t="inlineStr"/>
       <c r="AN2" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO2" s="8" t="inlineStr"/>
@@ -1285,13 +1285,13 @@
       <c r="AB3" s="8" t="inlineStr"/>
       <c r="AC3" s="8" t="inlineStr"/>
       <c r="AD3" s="9" t="n">
-        <v>46171.80208333334</v>
+        <v>46177.5</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46171.875</v>
+        <v>46177.5</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4544.87</v>
+        <v>4477.19</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="AH3" s="8" t="n">
-        <v>4520.79</v>
+        <v>4477.25</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>24.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>PD_FILL_FAIL</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr"/>
@@ -1337,554 +1337,8 @@
       <c r="BJ3" s="8" t="inlineStr"/>
       <c r="BK3" s="8" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="8" t="inlineStr"/>
-      <c r="V4" s="8" t="inlineStr"/>
-      <c r="W4" s="8" t="inlineStr"/>
-      <c r="X4" s="8" t="inlineStr"/>
-      <c r="Y4" s="8" t="inlineStr"/>
-      <c r="Z4" s="8" t="inlineStr"/>
-      <c r="AA4" s="8" t="inlineStr"/>
-      <c r="AB4" s="8" t="inlineStr"/>
-      <c r="AC4" s="8" t="inlineStr"/>
-      <c r="AD4" s="9" t="n">
-        <v>46172.11458333334</v>
-      </c>
-      <c r="AE4" s="9" t="n">
-        <v>46174.48958333334</v>
-      </c>
-      <c r="AF4" s="8" t="n">
-        <v>4509.08</v>
-      </c>
-      <c r="AG4" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH4" s="8" t="n">
-        <v>4543.27</v>
-      </c>
-      <c r="AI4" s="8" t="n">
-        <v>-34.19</v>
-      </c>
-      <c r="AJ4" s="8" t="inlineStr"/>
-      <c r="AK4" s="8" t="inlineStr"/>
-      <c r="AL4" s="8" t="inlineStr"/>
-      <c r="AM4" s="8" t="inlineStr"/>
-      <c r="AN4" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO4" s="8" t="inlineStr"/>
-      <c r="AP4" s="8" t="inlineStr"/>
-      <c r="AQ4" s="8" t="inlineStr"/>
-      <c r="AR4" s="8" t="inlineStr"/>
-      <c r="AS4" s="8" t="inlineStr"/>
-      <c r="AT4" s="8" t="inlineStr"/>
-      <c r="AU4" s="8" t="inlineStr"/>
-      <c r="AV4" s="8" t="inlineStr"/>
-      <c r="AW4" s="8" t="inlineStr"/>
-      <c r="AX4" s="8" t="inlineStr"/>
-      <c r="AY4" s="8" t="inlineStr"/>
-      <c r="AZ4" s="8" t="inlineStr"/>
-      <c r="BA4" s="8" t="inlineStr"/>
-      <c r="BB4" s="8" t="inlineStr"/>
-      <c r="BC4" s="8" t="inlineStr"/>
-      <c r="BD4" s="8" t="inlineStr"/>
-      <c r="BE4" s="8" t="inlineStr"/>
-      <c r="BF4" s="8" t="inlineStr"/>
-      <c r="BG4" s="8" t="inlineStr"/>
-      <c r="BH4" s="8" t="inlineStr"/>
-      <c r="BI4" s="8" t="inlineStr"/>
-      <c r="BJ4" s="8" t="inlineStr"/>
-      <c r="BK4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="8" t="inlineStr"/>
-      <c r="V5" s="8" t="inlineStr"/>
-      <c r="W5" s="8" t="inlineStr"/>
-      <c r="X5" s="8" t="inlineStr"/>
-      <c r="Y5" s="8" t="inlineStr"/>
-      <c r="Z5" s="8" t="inlineStr"/>
-      <c r="AA5" s="8" t="inlineStr"/>
-      <c r="AB5" s="8" t="inlineStr"/>
-      <c r="AC5" s="8" t="inlineStr"/>
-      <c r="AD5" s="9" t="n">
-        <v>46176.29166666666</v>
-      </c>
-      <c r="AE5" s="9" t="n">
-        <v>46176.60416666666</v>
-      </c>
-      <c r="AF5" s="8" t="n">
-        <v>4455.04</v>
-      </c>
-      <c r="AG5" s="8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH5" s="8" t="n">
-        <v>4478.73</v>
-      </c>
-      <c r="AI5" s="8" t="n">
-        <v>23.69</v>
-      </c>
-      <c r="AJ5" s="8" t="inlineStr"/>
-      <c r="AK5" s="8" t="inlineStr"/>
-      <c r="AL5" s="8" t="inlineStr"/>
-      <c r="AM5" s="8" t="inlineStr"/>
-      <c r="AN5" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO5" s="8" t="inlineStr"/>
-      <c r="AP5" s="8" t="inlineStr"/>
-      <c r="AQ5" s="8" t="inlineStr"/>
-      <c r="AR5" s="8" t="inlineStr"/>
-      <c r="AS5" s="8" t="inlineStr"/>
-      <c r="AT5" s="8" t="inlineStr"/>
-      <c r="AU5" s="8" t="inlineStr"/>
-      <c r="AV5" s="8" t="inlineStr"/>
-      <c r="AW5" s="8" t="inlineStr"/>
-      <c r="AX5" s="8" t="inlineStr"/>
-      <c r="AY5" s="8" t="inlineStr"/>
-      <c r="AZ5" s="8" t="inlineStr"/>
-      <c r="BA5" s="8" t="inlineStr"/>
-      <c r="BB5" s="8" t="inlineStr"/>
-      <c r="BC5" s="8" t="inlineStr"/>
-      <c r="BD5" s="8" t="inlineStr"/>
-      <c r="BE5" s="8" t="inlineStr"/>
-      <c r="BF5" s="8" t="inlineStr"/>
-      <c r="BG5" s="8" t="inlineStr"/>
-      <c r="BH5" s="8" t="inlineStr"/>
-      <c r="BI5" s="8" t="inlineStr"/>
-      <c r="BJ5" s="8" t="inlineStr"/>
-      <c r="BK5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
-      <c r="U6" s="8" t="inlineStr"/>
-      <c r="V6" s="8" t="inlineStr"/>
-      <c r="W6" s="8" t="inlineStr"/>
-      <c r="X6" s="8" t="inlineStr"/>
-      <c r="Y6" s="8" t="inlineStr"/>
-      <c r="Z6" s="8" t="inlineStr"/>
-      <c r="AA6" s="8" t="inlineStr"/>
-      <c r="AB6" s="8" t="inlineStr"/>
-      <c r="AC6" s="8" t="inlineStr"/>
-      <c r="AD6" s="9" t="n">
-        <v>46176.375</v>
-      </c>
-      <c r="AE6" s="9" t="n">
-        <v>46176.625</v>
-      </c>
-      <c r="AF6" s="8" t="n">
-        <v>4452.33</v>
-      </c>
-      <c r="AG6" s="8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH6" s="8" t="n">
-        <v>4478.73</v>
-      </c>
-      <c r="AI6" s="8" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AJ6" s="8" t="inlineStr"/>
-      <c r="AK6" s="8" t="inlineStr"/>
-      <c r="AL6" s="8" t="inlineStr"/>
-      <c r="AM6" s="8" t="inlineStr"/>
-      <c r="AN6" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO6" s="8" t="inlineStr"/>
-      <c r="AP6" s="8" t="inlineStr"/>
-      <c r="AQ6" s="8" t="inlineStr"/>
-      <c r="AR6" s="8" t="inlineStr"/>
-      <c r="AS6" s="8" t="inlineStr"/>
-      <c r="AT6" s="8" t="inlineStr"/>
-      <c r="AU6" s="8" t="inlineStr"/>
-      <c r="AV6" s="8" t="inlineStr"/>
-      <c r="AW6" s="8" t="inlineStr"/>
-      <c r="AX6" s="8" t="inlineStr"/>
-      <c r="AY6" s="8" t="inlineStr"/>
-      <c r="AZ6" s="8" t="inlineStr"/>
-      <c r="BA6" s="8" t="inlineStr"/>
-      <c r="BB6" s="8" t="inlineStr"/>
-      <c r="BC6" s="8" t="inlineStr"/>
-      <c r="BD6" s="8" t="inlineStr"/>
-      <c r="BE6" s="8" t="inlineStr"/>
-      <c r="BF6" s="8" t="inlineStr"/>
-      <c r="BG6" s="8" t="inlineStr"/>
-      <c r="BH6" s="8" t="inlineStr"/>
-      <c r="BI6" s="8" t="inlineStr"/>
-      <c r="BJ6" s="8" t="inlineStr"/>
-      <c r="BK6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="8" t="inlineStr"/>
-      <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="8" t="inlineStr"/>
-      <c r="S7" s="8" t="inlineStr"/>
-      <c r="T7" s="8" t="inlineStr"/>
-      <c r="U7" s="8" t="inlineStr"/>
-      <c r="V7" s="8" t="inlineStr"/>
-      <c r="W7" s="8" t="inlineStr"/>
-      <c r="X7" s="8" t="inlineStr"/>
-      <c r="Y7" s="8" t="inlineStr"/>
-      <c r="Z7" s="8" t="inlineStr"/>
-      <c r="AA7" s="8" t="inlineStr"/>
-      <c r="AB7" s="8" t="inlineStr"/>
-      <c r="AC7" s="8" t="inlineStr"/>
-      <c r="AD7" s="9" t="n">
-        <v>46177.42708333334</v>
-      </c>
-      <c r="AE7" s="9" t="n">
-        <v>46177.77083333334</v>
-      </c>
-      <c r="AF7" s="8" t="n">
-        <v>4491.31</v>
-      </c>
-      <c r="AG7" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH7" s="8" t="n">
-        <v>4467.44</v>
-      </c>
-      <c r="AI7" s="8" t="n">
-        <v>23.87</v>
-      </c>
-      <c r="AJ7" s="8" t="inlineStr"/>
-      <c r="AK7" s="8" t="inlineStr"/>
-      <c r="AL7" s="8" t="inlineStr"/>
-      <c r="AM7" s="8" t="inlineStr"/>
-      <c r="AN7" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO7" s="8" t="inlineStr"/>
-      <c r="AP7" s="8" t="inlineStr"/>
-      <c r="AQ7" s="8" t="inlineStr"/>
-      <c r="AR7" s="8" t="inlineStr"/>
-      <c r="AS7" s="8" t="inlineStr"/>
-      <c r="AT7" s="8" t="inlineStr"/>
-      <c r="AU7" s="8" t="inlineStr"/>
-      <c r="AV7" s="8" t="inlineStr"/>
-      <c r="AW7" s="8" t="inlineStr"/>
-      <c r="AX7" s="8" t="inlineStr"/>
-      <c r="AY7" s="8" t="inlineStr"/>
-      <c r="AZ7" s="8" t="inlineStr"/>
-      <c r="BA7" s="8" t="inlineStr"/>
-      <c r="BB7" s="8" t="inlineStr"/>
-      <c r="BC7" s="8" t="inlineStr"/>
-      <c r="BD7" s="8" t="inlineStr"/>
-      <c r="BE7" s="8" t="inlineStr"/>
-      <c r="BF7" s="8" t="inlineStr"/>
-      <c r="BG7" s="8" t="inlineStr"/>
-      <c r="BH7" s="8" t="inlineStr"/>
-      <c r="BI7" s="8" t="inlineStr"/>
-      <c r="BJ7" s="8" t="inlineStr"/>
-      <c r="BK7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
-      <c r="S8" s="8" t="inlineStr"/>
-      <c r="T8" s="8" t="inlineStr"/>
-      <c r="U8" s="8" t="inlineStr"/>
-      <c r="V8" s="8" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr"/>
-      <c r="X8" s="8" t="inlineStr"/>
-      <c r="Y8" s="8" t="inlineStr"/>
-      <c r="Z8" s="8" t="inlineStr"/>
-      <c r="AA8" s="8" t="inlineStr"/>
-      <c r="AB8" s="8" t="inlineStr"/>
-      <c r="AC8" s="8" t="inlineStr"/>
-      <c r="AD8" s="9" t="n">
-        <v>46177.5</v>
-      </c>
-      <c r="AE8" s="9" t="n">
-        <v>46177.78125</v>
-      </c>
-      <c r="AF8" s="8" t="n">
-        <v>4497.03</v>
-      </c>
-      <c r="AG8" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH8" s="8" t="n">
-        <v>4477.25</v>
-      </c>
-      <c r="AI8" s="8" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="AJ8" s="8" t="inlineStr"/>
-      <c r="AK8" s="8" t="inlineStr"/>
-      <c r="AL8" s="8" t="inlineStr"/>
-      <c r="AM8" s="8" t="inlineStr"/>
-      <c r="AN8" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO8" s="8" t="inlineStr"/>
-      <c r="AP8" s="8" t="inlineStr"/>
-      <c r="AQ8" s="8" t="inlineStr"/>
-      <c r="AR8" s="8" t="inlineStr"/>
-      <c r="AS8" s="8" t="inlineStr"/>
-      <c r="AT8" s="8" t="inlineStr"/>
-      <c r="AU8" s="8" t="inlineStr"/>
-      <c r="AV8" s="8" t="inlineStr"/>
-      <c r="AW8" s="8" t="inlineStr"/>
-      <c r="AX8" s="8" t="inlineStr"/>
-      <c r="AY8" s="8" t="inlineStr"/>
-      <c r="AZ8" s="8" t="inlineStr"/>
-      <c r="BA8" s="8" t="inlineStr"/>
-      <c r="BB8" s="8" t="inlineStr"/>
-      <c r="BC8" s="8" t="inlineStr"/>
-      <c r="BD8" s="8" t="inlineStr"/>
-      <c r="BE8" s="8" t="inlineStr"/>
-      <c r="BF8" s="8" t="inlineStr"/>
-      <c r="BG8" s="8" t="inlineStr"/>
-      <c r="BH8" s="8" t="inlineStr"/>
-      <c r="BI8" s="8" t="inlineStr"/>
-      <c r="BJ8" s="8" t="inlineStr"/>
-      <c r="BK8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="8" t="inlineStr"/>
-      <c r="S9" s="8" t="inlineStr"/>
-      <c r="T9" s="8" t="inlineStr"/>
-      <c r="U9" s="8" t="inlineStr"/>
-      <c r="V9" s="8" t="inlineStr"/>
-      <c r="W9" s="8" t="inlineStr"/>
-      <c r="X9" s="8" t="inlineStr"/>
-      <c r="Y9" s="8" t="inlineStr"/>
-      <c r="Z9" s="8" t="inlineStr"/>
-      <c r="AA9" s="8" t="inlineStr"/>
-      <c r="AB9" s="8" t="inlineStr"/>
-      <c r="AC9" s="8" t="inlineStr"/>
-      <c r="AD9" s="9" t="n">
-        <v>46178.83333333334</v>
-      </c>
-      <c r="AE9" s="9" t="n">
-        <v>46178.86458333334</v>
-      </c>
-      <c r="AF9" s="8" t="n">
-        <v>4378.5</v>
-      </c>
-      <c r="AG9" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH9" s="8" t="n">
-        <v>4404.2</v>
-      </c>
-      <c r="AI9" s="8" t="n">
-        <v>-25.7</v>
-      </c>
-      <c r="AJ9" s="8" t="inlineStr"/>
-      <c r="AK9" s="8" t="inlineStr"/>
-      <c r="AL9" s="8" t="inlineStr"/>
-      <c r="AM9" s="8" t="inlineStr"/>
-      <c r="AN9" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO9" s="8" t="inlineStr"/>
-      <c r="AP9" s="8" t="inlineStr"/>
-      <c r="AQ9" s="8" t="inlineStr"/>
-      <c r="AR9" s="8" t="inlineStr"/>
-      <c r="AS9" s="8" t="inlineStr"/>
-      <c r="AT9" s="8" t="inlineStr"/>
-      <c r="AU9" s="8" t="inlineStr"/>
-      <c r="AV9" s="8" t="inlineStr"/>
-      <c r="AW9" s="8" t="inlineStr"/>
-      <c r="AX9" s="8" t="inlineStr"/>
-      <c r="AY9" s="8" t="inlineStr"/>
-      <c r="AZ9" s="8" t="inlineStr"/>
-      <c r="BA9" s="8" t="inlineStr"/>
-      <c r="BB9" s="8" t="inlineStr"/>
-      <c r="BC9" s="8" t="inlineStr"/>
-      <c r="BD9" s="8" t="inlineStr"/>
-      <c r="BE9" s="8" t="inlineStr"/>
-      <c r="BF9" s="8" t="inlineStr"/>
-      <c r="BG9" s="8" t="inlineStr"/>
-      <c r="BH9" s="8" t="inlineStr"/>
-      <c r="BI9" s="8" t="inlineStr"/>
-      <c r="BJ9" s="8" t="inlineStr"/>
-      <c r="BK9" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BK9"/>
+  <autoFilter ref="A1:BK3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2819,7 +2273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK9"/>
+  <dimension ref="A1:BK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2861,7 +2315,7 @@
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
     <col width="15" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="15" customWidth="1" min="43" max="43"/>
@@ -3243,24 +2697,24 @@
       <c r="AB2" s="8" t="inlineStr"/>
       <c r="AC2" s="8" t="inlineStr"/>
       <c r="AD2" s="9" t="n">
-        <v>46171.625</v>
+        <v>46170.875</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>46171.875</v>
+        <v>46170.90625</v>
       </c>
       <c r="AF2" s="8" t="n">
-        <v>4544.3</v>
+        <v>4477.22</v>
       </c>
       <c r="AG2" s="8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH2" s="8" t="n">
-        <v>4520.79</v>
+        <v>4448.91</v>
       </c>
       <c r="AI2" s="8" t="n">
-        <v>23.51</v>
+        <v>-28.31</v>
       </c>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
@@ -3268,7 +2722,7 @@
       <c r="AM2" s="8" t="inlineStr"/>
       <c r="AN2" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO2" s="8" t="inlineStr"/>
@@ -3334,13 +2788,13 @@
       <c r="AB3" s="8" t="inlineStr"/>
       <c r="AC3" s="8" t="inlineStr"/>
       <c r="AD3" s="9" t="n">
-        <v>46171.80208333334</v>
+        <v>46177.5</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>46171.875</v>
+        <v>46177.5</v>
       </c>
       <c r="AF3" s="8" t="n">
-        <v>4544.87</v>
+        <v>4477.19</v>
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
@@ -3348,10 +2802,10 @@
         </is>
       </c>
       <c r="AH3" s="8" t="n">
-        <v>4520.79</v>
+        <v>4477.25</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>24.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AJ3" s="8" t="inlineStr"/>
       <c r="AK3" s="8" t="inlineStr"/>
@@ -3359,7 +2813,7 @@
       <c r="AM3" s="8" t="inlineStr"/>
       <c r="AN3" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>PD_FILL_FAIL</t>
         </is>
       </c>
       <c r="AO3" s="8" t="inlineStr"/>
@@ -3386,554 +2840,8 @@
       <c r="BJ3" s="8" t="inlineStr"/>
       <c r="BK3" s="8" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="8" t="inlineStr"/>
-      <c r="V4" s="8" t="inlineStr"/>
-      <c r="W4" s="8" t="inlineStr"/>
-      <c r="X4" s="8" t="inlineStr"/>
-      <c r="Y4" s="8" t="inlineStr"/>
-      <c r="Z4" s="8" t="inlineStr"/>
-      <c r="AA4" s="8" t="inlineStr"/>
-      <c r="AB4" s="8" t="inlineStr"/>
-      <c r="AC4" s="8" t="inlineStr"/>
-      <c r="AD4" s="9" t="n">
-        <v>46172.11458333334</v>
-      </c>
-      <c r="AE4" s="9" t="n">
-        <v>46174.48958333334</v>
-      </c>
-      <c r="AF4" s="8" t="n">
-        <v>4509.08</v>
-      </c>
-      <c r="AG4" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH4" s="8" t="n">
-        <v>4543.27</v>
-      </c>
-      <c r="AI4" s="8" t="n">
-        <v>-34.19</v>
-      </c>
-      <c r="AJ4" s="8" t="inlineStr"/>
-      <c r="AK4" s="8" t="inlineStr"/>
-      <c r="AL4" s="8" t="inlineStr"/>
-      <c r="AM4" s="8" t="inlineStr"/>
-      <c r="AN4" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO4" s="8" t="inlineStr"/>
-      <c r="AP4" s="8" t="inlineStr"/>
-      <c r="AQ4" s="8" t="inlineStr"/>
-      <c r="AR4" s="8" t="inlineStr"/>
-      <c r="AS4" s="8" t="inlineStr"/>
-      <c r="AT4" s="8" t="inlineStr"/>
-      <c r="AU4" s="8" t="inlineStr"/>
-      <c r="AV4" s="8" t="inlineStr"/>
-      <c r="AW4" s="8" t="inlineStr"/>
-      <c r="AX4" s="8" t="inlineStr"/>
-      <c r="AY4" s="8" t="inlineStr"/>
-      <c r="AZ4" s="8" t="inlineStr"/>
-      <c r="BA4" s="8" t="inlineStr"/>
-      <c r="BB4" s="8" t="inlineStr"/>
-      <c r="BC4" s="8" t="inlineStr"/>
-      <c r="BD4" s="8" t="inlineStr"/>
-      <c r="BE4" s="8" t="inlineStr"/>
-      <c r="BF4" s="8" t="inlineStr"/>
-      <c r="BG4" s="8" t="inlineStr"/>
-      <c r="BH4" s="8" t="inlineStr"/>
-      <c r="BI4" s="8" t="inlineStr"/>
-      <c r="BJ4" s="8" t="inlineStr"/>
-      <c r="BK4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="8" t="inlineStr"/>
-      <c r="V5" s="8" t="inlineStr"/>
-      <c r="W5" s="8" t="inlineStr"/>
-      <c r="X5" s="8" t="inlineStr"/>
-      <c r="Y5" s="8" t="inlineStr"/>
-      <c r="Z5" s="8" t="inlineStr"/>
-      <c r="AA5" s="8" t="inlineStr"/>
-      <c r="AB5" s="8" t="inlineStr"/>
-      <c r="AC5" s="8" t="inlineStr"/>
-      <c r="AD5" s="9" t="n">
-        <v>46176.29166666666</v>
-      </c>
-      <c r="AE5" s="9" t="n">
-        <v>46176.60416666666</v>
-      </c>
-      <c r="AF5" s="8" t="n">
-        <v>4455.04</v>
-      </c>
-      <c r="AG5" s="8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH5" s="8" t="n">
-        <v>4478.73</v>
-      </c>
-      <c r="AI5" s="8" t="n">
-        <v>23.69</v>
-      </c>
-      <c r="AJ5" s="8" t="inlineStr"/>
-      <c r="AK5" s="8" t="inlineStr"/>
-      <c r="AL5" s="8" t="inlineStr"/>
-      <c r="AM5" s="8" t="inlineStr"/>
-      <c r="AN5" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO5" s="8" t="inlineStr"/>
-      <c r="AP5" s="8" t="inlineStr"/>
-      <c r="AQ5" s="8" t="inlineStr"/>
-      <c r="AR5" s="8" t="inlineStr"/>
-      <c r="AS5" s="8" t="inlineStr"/>
-      <c r="AT5" s="8" t="inlineStr"/>
-      <c r="AU5" s="8" t="inlineStr"/>
-      <c r="AV5" s="8" t="inlineStr"/>
-      <c r="AW5" s="8" t="inlineStr"/>
-      <c r="AX5" s="8" t="inlineStr"/>
-      <c r="AY5" s="8" t="inlineStr"/>
-      <c r="AZ5" s="8" t="inlineStr"/>
-      <c r="BA5" s="8" t="inlineStr"/>
-      <c r="BB5" s="8" t="inlineStr"/>
-      <c r="BC5" s="8" t="inlineStr"/>
-      <c r="BD5" s="8" t="inlineStr"/>
-      <c r="BE5" s="8" t="inlineStr"/>
-      <c r="BF5" s="8" t="inlineStr"/>
-      <c r="BG5" s="8" t="inlineStr"/>
-      <c r="BH5" s="8" t="inlineStr"/>
-      <c r="BI5" s="8" t="inlineStr"/>
-      <c r="BJ5" s="8" t="inlineStr"/>
-      <c r="BK5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
-      <c r="U6" s="8" t="inlineStr"/>
-      <c r="V6" s="8" t="inlineStr"/>
-      <c r="W6" s="8" t="inlineStr"/>
-      <c r="X6" s="8" t="inlineStr"/>
-      <c r="Y6" s="8" t="inlineStr"/>
-      <c r="Z6" s="8" t="inlineStr"/>
-      <c r="AA6" s="8" t="inlineStr"/>
-      <c r="AB6" s="8" t="inlineStr"/>
-      <c r="AC6" s="8" t="inlineStr"/>
-      <c r="AD6" s="9" t="n">
-        <v>46176.375</v>
-      </c>
-      <c r="AE6" s="9" t="n">
-        <v>46176.625</v>
-      </c>
-      <c r="AF6" s="8" t="n">
-        <v>4452.33</v>
-      </c>
-      <c r="AG6" s="8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH6" s="8" t="n">
-        <v>4478.73</v>
-      </c>
-      <c r="AI6" s="8" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AJ6" s="8" t="inlineStr"/>
-      <c r="AK6" s="8" t="inlineStr"/>
-      <c r="AL6" s="8" t="inlineStr"/>
-      <c r="AM6" s="8" t="inlineStr"/>
-      <c r="AN6" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO6" s="8" t="inlineStr"/>
-      <c r="AP6" s="8" t="inlineStr"/>
-      <c r="AQ6" s="8" t="inlineStr"/>
-      <c r="AR6" s="8" t="inlineStr"/>
-      <c r="AS6" s="8" t="inlineStr"/>
-      <c r="AT6" s="8" t="inlineStr"/>
-      <c r="AU6" s="8" t="inlineStr"/>
-      <c r="AV6" s="8" t="inlineStr"/>
-      <c r="AW6" s="8" t="inlineStr"/>
-      <c r="AX6" s="8" t="inlineStr"/>
-      <c r="AY6" s="8" t="inlineStr"/>
-      <c r="AZ6" s="8" t="inlineStr"/>
-      <c r="BA6" s="8" t="inlineStr"/>
-      <c r="BB6" s="8" t="inlineStr"/>
-      <c r="BC6" s="8" t="inlineStr"/>
-      <c r="BD6" s="8" t="inlineStr"/>
-      <c r="BE6" s="8" t="inlineStr"/>
-      <c r="BF6" s="8" t="inlineStr"/>
-      <c r="BG6" s="8" t="inlineStr"/>
-      <c r="BH6" s="8" t="inlineStr"/>
-      <c r="BI6" s="8" t="inlineStr"/>
-      <c r="BJ6" s="8" t="inlineStr"/>
-      <c r="BK6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="8" t="inlineStr"/>
-      <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="8" t="inlineStr"/>
-      <c r="S7" s="8" t="inlineStr"/>
-      <c r="T7" s="8" t="inlineStr"/>
-      <c r="U7" s="8" t="inlineStr"/>
-      <c r="V7" s="8" t="inlineStr"/>
-      <c r="W7" s="8" t="inlineStr"/>
-      <c r="X7" s="8" t="inlineStr"/>
-      <c r="Y7" s="8" t="inlineStr"/>
-      <c r="Z7" s="8" t="inlineStr"/>
-      <c r="AA7" s="8" t="inlineStr"/>
-      <c r="AB7" s="8" t="inlineStr"/>
-      <c r="AC7" s="8" t="inlineStr"/>
-      <c r="AD7" s="9" t="n">
-        <v>46177.42708333334</v>
-      </c>
-      <c r="AE7" s="9" t="n">
-        <v>46177.77083333334</v>
-      </c>
-      <c r="AF7" s="8" t="n">
-        <v>4491.31</v>
-      </c>
-      <c r="AG7" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH7" s="8" t="n">
-        <v>4467.44</v>
-      </c>
-      <c r="AI7" s="8" t="n">
-        <v>23.87</v>
-      </c>
-      <c r="AJ7" s="8" t="inlineStr"/>
-      <c r="AK7" s="8" t="inlineStr"/>
-      <c r="AL7" s="8" t="inlineStr"/>
-      <c r="AM7" s="8" t="inlineStr"/>
-      <c r="AN7" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO7" s="8" t="inlineStr"/>
-      <c r="AP7" s="8" t="inlineStr"/>
-      <c r="AQ7" s="8" t="inlineStr"/>
-      <c r="AR7" s="8" t="inlineStr"/>
-      <c r="AS7" s="8" t="inlineStr"/>
-      <c r="AT7" s="8" t="inlineStr"/>
-      <c r="AU7" s="8" t="inlineStr"/>
-      <c r="AV7" s="8" t="inlineStr"/>
-      <c r="AW7" s="8" t="inlineStr"/>
-      <c r="AX7" s="8" t="inlineStr"/>
-      <c r="AY7" s="8" t="inlineStr"/>
-      <c r="AZ7" s="8" t="inlineStr"/>
-      <c r="BA7" s="8" t="inlineStr"/>
-      <c r="BB7" s="8" t="inlineStr"/>
-      <c r="BC7" s="8" t="inlineStr"/>
-      <c r="BD7" s="8" t="inlineStr"/>
-      <c r="BE7" s="8" t="inlineStr"/>
-      <c r="BF7" s="8" t="inlineStr"/>
-      <c r="BG7" s="8" t="inlineStr"/>
-      <c r="BH7" s="8" t="inlineStr"/>
-      <c r="BI7" s="8" t="inlineStr"/>
-      <c r="BJ7" s="8" t="inlineStr"/>
-      <c r="BK7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
-      <c r="S8" s="8" t="inlineStr"/>
-      <c r="T8" s="8" t="inlineStr"/>
-      <c r="U8" s="8" t="inlineStr"/>
-      <c r="V8" s="8" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr"/>
-      <c r="X8" s="8" t="inlineStr"/>
-      <c r="Y8" s="8" t="inlineStr"/>
-      <c r="Z8" s="8" t="inlineStr"/>
-      <c r="AA8" s="8" t="inlineStr"/>
-      <c r="AB8" s="8" t="inlineStr"/>
-      <c r="AC8" s="8" t="inlineStr"/>
-      <c r="AD8" s="9" t="n">
-        <v>46177.5</v>
-      </c>
-      <c r="AE8" s="9" t="n">
-        <v>46177.78125</v>
-      </c>
-      <c r="AF8" s="8" t="n">
-        <v>4497.03</v>
-      </c>
-      <c r="AG8" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH8" s="8" t="n">
-        <v>4477.25</v>
-      </c>
-      <c r="AI8" s="8" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="AJ8" s="8" t="inlineStr"/>
-      <c r="AK8" s="8" t="inlineStr"/>
-      <c r="AL8" s="8" t="inlineStr"/>
-      <c r="AM8" s="8" t="inlineStr"/>
-      <c r="AN8" s="8" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO8" s="8" t="inlineStr"/>
-      <c r="AP8" s="8" t="inlineStr"/>
-      <c r="AQ8" s="8" t="inlineStr"/>
-      <c r="AR8" s="8" t="inlineStr"/>
-      <c r="AS8" s="8" t="inlineStr"/>
-      <c r="AT8" s="8" t="inlineStr"/>
-      <c r="AU8" s="8" t="inlineStr"/>
-      <c r="AV8" s="8" t="inlineStr"/>
-      <c r="AW8" s="8" t="inlineStr"/>
-      <c r="AX8" s="8" t="inlineStr"/>
-      <c r="AY8" s="8" t="inlineStr"/>
-      <c r="AZ8" s="8" t="inlineStr"/>
-      <c r="BA8" s="8" t="inlineStr"/>
-      <c r="BB8" s="8" t="inlineStr"/>
-      <c r="BC8" s="8" t="inlineStr"/>
-      <c r="BD8" s="8" t="inlineStr"/>
-      <c r="BE8" s="8" t="inlineStr"/>
-      <c r="BF8" s="8" t="inlineStr"/>
-      <c r="BG8" s="8" t="inlineStr"/>
-      <c r="BH8" s="8" t="inlineStr"/>
-      <c r="BI8" s="8" t="inlineStr"/>
-      <c r="BJ8" s="8" t="inlineStr"/>
-      <c r="BK8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="8" t="inlineStr"/>
-      <c r="S9" s="8" t="inlineStr"/>
-      <c r="T9" s="8" t="inlineStr"/>
-      <c r="U9" s="8" t="inlineStr"/>
-      <c r="V9" s="8" t="inlineStr"/>
-      <c r="W9" s="8" t="inlineStr"/>
-      <c r="X9" s="8" t="inlineStr"/>
-      <c r="Y9" s="8" t="inlineStr"/>
-      <c r="Z9" s="8" t="inlineStr"/>
-      <c r="AA9" s="8" t="inlineStr"/>
-      <c r="AB9" s="8" t="inlineStr"/>
-      <c r="AC9" s="8" t="inlineStr"/>
-      <c r="AD9" s="9" t="n">
-        <v>46178.83333333334</v>
-      </c>
-      <c r="AE9" s="9" t="n">
-        <v>46178.86458333334</v>
-      </c>
-      <c r="AF9" s="8" t="n">
-        <v>4378.5</v>
-      </c>
-      <c r="AG9" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH9" s="8" t="n">
-        <v>4404.2</v>
-      </c>
-      <c r="AI9" s="8" t="n">
-        <v>-25.7</v>
-      </c>
-      <c r="AJ9" s="8" t="inlineStr"/>
-      <c r="AK9" s="8" t="inlineStr"/>
-      <c r="AL9" s="8" t="inlineStr"/>
-      <c r="AM9" s="8" t="inlineStr"/>
-      <c r="AN9" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO9" s="8" t="inlineStr"/>
-      <c r="AP9" s="8" t="inlineStr"/>
-      <c r="AQ9" s="8" t="inlineStr"/>
-      <c r="AR9" s="8" t="inlineStr"/>
-      <c r="AS9" s="8" t="inlineStr"/>
-      <c r="AT9" s="8" t="inlineStr"/>
-      <c r="AU9" s="8" t="inlineStr"/>
-      <c r="AV9" s="8" t="inlineStr"/>
-      <c r="AW9" s="8" t="inlineStr"/>
-      <c r="AX9" s="8" t="inlineStr"/>
-      <c r="AY9" s="8" t="inlineStr"/>
-      <c r="AZ9" s="8" t="inlineStr"/>
-      <c r="BA9" s="8" t="inlineStr"/>
-      <c r="BB9" s="8" t="inlineStr"/>
-      <c r="BC9" s="8" t="inlineStr"/>
-      <c r="BD9" s="8" t="inlineStr"/>
-      <c r="BE9" s="8" t="inlineStr"/>
-      <c r="BF9" s="8" t="inlineStr"/>
-      <c r="BG9" s="8" t="inlineStr"/>
-      <c r="BH9" s="8" t="inlineStr"/>
-      <c r="BI9" s="8" t="inlineStr"/>
-      <c r="BJ9" s="8" t="inlineStr"/>
-      <c r="BK9" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BK9"/>
+  <autoFilter ref="A1:BK3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4406,7 +3314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4463,7 +3371,7 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>PD_FILL_FAIL</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -4472,13 +3380,13 @@
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>91.23999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>46171.625</v>
+        <v>46177.5</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>46177.5</v>
@@ -4497,31 +3405,31 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-59.89</v>
+        <v>-28.31</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>46172.11458333334</v>
+        <v>46170.875</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>46178.83333333334</v>
+        <v>46170.875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>bt</t>
+          <t>bt_gap</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>NO_SAME_SIDE_CANDIDATE</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -4533,24 +3441,24 @@
         <v>2</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>50.09</v>
+        <v>-28.37</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>46176.29166666666</v>
+        <v>46170.875</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>46176.375</v>
+        <v>46177.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>bt_gap</t>
+          <t>bt_s14_family</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -4559,16 +3467,16 @@
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>81.44</v>
+        <v>-0.06</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>46171.625</v>
+        <v>46177.5</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>46178.83333333334</v>
+        <v>46177.5</v>
       </c>
     </row>
     <row r="6">
@@ -4584,53 +3492,24 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>31.35</v>
+        <v>-28.31</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>46171.625</v>
+        <v>46170.875</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>46178.83333333334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>46176.29166666666</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>46176.375</v>
+        <v>46170.875</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>